--- a/docs/Revenue_Opportunity_Regression.xlsx
+++ b/docs/Revenue_Opportunity_Regression.xlsx
@@ -13,9 +13,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="194">
-  <si>
-    <t>Profile: US / GDC Test Site 2 | Type: Regression (read-only) | Total TCs: 35 | Revenue Opportunity</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="212">
+  <si>
+    <t>Profile: US / GDC Test Site 2 | Type: Regression (read-only) | Total TCs: 39 | Revenue Opportunity</t>
   </si>
   <si>
     <t>Confluence: https://bluetriangletech.atlassian.net/wiki/spaces/HCT/pages/3186360451/The+Revenue+Opportunity+Page</t>
@@ -48,6 +48,12 @@
     <t>REG-RO-019, REG-RO-020, REG-RO-021, REG-RO-032</t>
   </si>
   <si>
+    <t>Time Period</t>
+  </si>
+  <si>
+    <t>REG-RO-036, REG-RO-037, REG-RO-038, REG-RO-039</t>
+  </si>
+  <si>
     <t>Revenue Data Type</t>
   </si>
   <si>
@@ -153,7 +159,7 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>REG-RO-001 .. REG-RO-035</t>
+    <t>REG-RO-001 .. REG-RO-039</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -665,6 +671,75 @@
     <t>Calibration control is visible with a tooltip</t>
   </si>
   <si>
+    <t>REG-RO-036</t>
+  </si>
+  <si>
+    <t>REG-RO-036 — Time Period 1 Days: labels + Actual Revenue timeline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open Revenue Opportunity (no Bucket Size control on this page)
+2. Apply Time Period = 1 Day via matching Report (e.g. "… 1 Day …") or Filters Time Period if available
+3. Confirm Opportunity / Actual Revenue Over Time / What If labels mention 1 Day
+4. Hover Actual Revenue Over Time left→right
+5. Validate Highcharts x-axis day buckets (~1 day steps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period applied via Report list and/or Filters Time Period only (no Bucket Size)
+Labels show 1 Day Opportunity / Actual Revenue Over Time period text
+What If / opportunity widgets mention 1 day when present
+Actual Revenue timeline uses ~1-day buckets ending near now
+If no 1-day report exists on the site, soft-skip with note</t>
+  </si>
+  <si>
+    <t>REG-RO-037</t>
+  </si>
+  <si>
+    <t>REG-RO-037 — Time Period 7 Days: labels + Actual Revenue timeline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Apply Time Period = 7 Days via Report matching "7 Days" (or Filters)
+2. Confirm Opportunity / Actual Revenue / What If period labels
+3. Hover Actual Revenue; validate ~1-day timeline buckets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Bucket Size selection (control not present on Revenue Opportunity)
+Labels and widgets reflect 7 Days
+Actual Revenue timeline remains healthy with day-scale buckets</t>
+  </si>
+  <si>
+    <t>REG-RO-038</t>
+  </si>
+  <si>
+    <t>REG-RO-038 — Time Period 14 Days: labels + Actual Revenue timeline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Apply Time Period = 14 Days via Report / Filters
+2. Confirm period labels on Opportunity, Actual Revenue Over Time, What If
+3. Validate Actual Revenue timeline buckets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period applied without Bucket Size
+UI labels mention 14 Days
+Timeline buckets remain ~1 day for multi-day reports</t>
+  </si>
+  <si>
+    <t>REG-RO-039</t>
+  </si>
+  <si>
+    <t>REG-RO-039 — Time Period 30 days: labels + Actual Revenue timeline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Apply Time Period = 30 Days via Report matching "30 Days" (common default report)
+2. Confirm "30 Day Opportunity" and Actual Revenue Over Time period text
+3. Confirm What If widgets mention 30 days when labeled
+4. Hover Actual Revenue; validate day buckets near now</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30-day report/period applies; no Bucket Size control used
+Opportunity / Actual Revenue / What If labels align with 30 days
+Actual Revenue Over Time uses ~1-day Highcharts buckets ending near local now</t>
+  </si>
+  <si>
     <t>Blue Triangle Portal — Revenue Opportunity Regression Test Cases</t>
   </si>
   <si>
@@ -677,10 +752,10 @@
     <t>Columns: Test Case ID | Type | Module | Submodule | Title | Steps | Expected Results | Status</t>
   </si>
   <si>
-    <t>Total cases: 35</t>
-  </si>
-  <si>
-    <t>Automation: tests/regression_tests/US2/revenue.opportunity.regression.spec.ts</t>
+    <t>Total cases: 39</t>
+  </si>
+  <si>
+    <t>Automation: tests/regression_tests/US2/business-insights/improve-conversion/revenue-opportunity/revenue.opportunity.regression.spec.ts</t>
   </si>
 </sst>
 </file>
@@ -1093,7 +1168,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -1168,7 +1243,7 @@
         <v>11</v>
       </c>
       <c r="D6" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>12</v>
@@ -1224,7 +1299,7 @@
         <v>19</v>
       </c>
       <c r="D10" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>20</v>
@@ -1308,7 +1383,7 @@
         <v>31</v>
       </c>
       <c r="D16" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>32</v>
@@ -1398,18 +1473,32 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="5" t="s">
+    <row r="23" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="D23" s="4">
+        <v>1</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D23" s="5">
-        <v>35</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>46</v>
+      <c r="D24" s="5">
+        <v>39</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1424,7 +1513,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1438,10 +1527,10 @@
   <sheetData>
     <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
@@ -1450,492 +1539,492 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>8</v>
@@ -1944,24 +2033,24 @@
         <v>9</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>8</v>
@@ -1970,24 +2059,24 @@
         <v>9</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>8</v>
@@ -1996,284 +2085,284 @@
         <v>9</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>8</v>
@@ -2282,102 +2371,206 @@
         <v>9</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="38" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="39" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="40" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="H10:H36">
+    <dataValidation type="list" allowBlank="1" sqref="H10:H40">
       <formula1>"Not Executed,Pass,Fail,Blocked,Skipped"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H2:H36">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H40">
       <formula1>"Not Executed,Pass,Fail,Blocked,Skipped"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2396,27 +2589,27 @@
   <sheetData>
     <row r="1" spans="1:1" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
@@ -2426,7 +2619,7 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Revenue_Opportunity_Regression.xlsx
+++ b/docs/Revenue_Opportunity_Regression.xlsx
@@ -1,12 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4BC6827-0D5A-455F-ACC9-E64E80DC7D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Summary" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Regression TCs" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Notes" state="visible" r:id="rId6"/>
+    <sheet name="Summary" sheetId="1" r:id="rId1"/>
+    <sheet name="Regression TCs" sheetId="2" r:id="rId2"/>
+    <sheet name="Notes" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -186,13 +190,13 @@
     <t>REG-RO-001 — Page loads via menu/route with correct breadcrumb</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Login to Blue Triangle portal
+    <t>1. Login to Blue Triangle portal
 2. Ensure site is "GDC Test Site 2" (US)
 3. Open left nav: Business Insights &gt; Improve Conversion &gt; Revenue Opportunity (or Favorites shortcut if present)
 4. Observe breadcrumb and URL</t>
   </si>
   <si>
-    <t xml:space="preserve">Breadcrumb shows Business Insights / Improve Conversion / Revenue Opportunity
+    <t>Breadcrumb shows Business Insights / Improve Conversion / Revenue Opportunity
 URL contains business-analytics/revenue-opportunity
 User remains authenticated</t>
   </si>
@@ -203,12 +207,12 @@
     <t>REG-RO-002 — Default report/session context renders opportunity widgets</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Open Revenue Opportunity
+    <t>1. Open Revenue Opportunity
 2. Note the default selected Report in the Report dropdown
 3. Observe 30 Day Opportunity cards and charts</t>
   </si>
   <si>
-    <t xml:space="preserve">A default report is selected
+    <t>A default report is selected
 Top opportunity / device cards are visible
 Highcharts containers render with data</t>
   </si>
@@ -219,11 +223,11 @@
     <t>REG-RO-003 — Page load performance: title + charts within SLA window</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Navigate to Revenue Opportunity from a warm session
+    <t>1. Navigate to Revenue Opportunity from a warm session
 2. Measure time until title and charts are ready</t>
   </si>
   <si>
-    <t xml:space="preserve">Page becomes interactive with charts within 120 seconds
+    <t>Page becomes interactive with charts within 120 seconds
 No blank shell / login redirect</t>
   </si>
   <si>
@@ -233,11 +237,11 @@
     <t>REG-RO-004 — Revenue Data Type: Web Browser Data refreshes widgets</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Set Revenue Data Type to Web Browser Data
+    <t>1. Set Revenue Data Type to Web Browser Data
 2. Wait for widgets/charts to refresh</t>
   </si>
   <si>
-    <t xml:space="preserve">Charts refresh successfully
+    <t>Charts refresh successfully
 Page title remains Revenue Opportunity</t>
   </si>
   <si>
@@ -247,11 +251,11 @@
     <t>REG-RO-005 — Revenue Data Type: Native App Data sample</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Set Revenue Data Type to Native App Data (if configured for site)
+    <t>1. Set Revenue Data Type to Native App Data (if configured for site)
 2. Observe refresh; if unavailable, fall back to Web Browser Data</t>
   </si>
   <si>
-    <t xml:space="preserve">Native App Data applies when configured OR fallback keeps page healthy
+    <t>Native App Data applies when configured OR fallback keeps page healthy
 Charts remain populated</t>
   </si>
   <si>
@@ -261,11 +265,11 @@
     <t>REG-RO-006 — Revenue Data Type: Web Browser &amp; Native App combination</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Select combined Web Browser &amp; Native App data type
+    <t>1. Select combined Web Browser &amp; Native App data type
 2. Confirm widgets refresh</t>
   </si>
   <si>
-    <t xml:space="preserve">Combined data type applies or safe fallback occurs
+    <t>Combined data type applies or safe fallback occurs
 Charts show data</t>
   </si>
   <si>
@@ -275,11 +279,11 @@
     <t>REG-RO-007 — Report Type sample combination refreshes page</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Change Report Type (e.g. Page Name)
+    <t>1. Change Report Type (e.g. Page Name)
 2. Change to another type if available (CWV Selector)</t>
   </si>
   <si>
-    <t xml:space="preserve">Report Type changes refresh page content
+    <t>Report Type changes refresh page content
 Charts remain healthy</t>
   </si>
   <si>
@@ -289,11 +293,11 @@
     <t>REG-RO-008 — Report dropdown: switch to second available report</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Open Report dropdown
+    <t>1. Open Report dropdown
 2. Select the second listed report (if more than one exists)</t>
   </si>
   <si>
-    <t xml:space="preserve">Selected report loads
+    <t>Selected report loads
 Opportunity widgets refresh</t>
   </si>
   <si>
@@ -303,11 +307,11 @@
     <t>REG-RO-009 — Restore primary/default report (index 0)</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Select the first report in the Report list
+    <t>1. Select the first report in the Report list
 2. Confirm default-ish context returns</t>
   </si>
   <si>
-    <t xml:space="preserve">First report is active
+    <t>First report is active
 Default opportunity context is visible</t>
   </si>
   <si>
@@ -317,13 +321,13 @@
     <t>REG-RO-010 — All / Desktop / Mobile card clicks refresh sections</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click All / Browser opportunity card
+    <t>1. Click All / Browser opportunity card
 2. Click Desktop card
 3. Click Mobile card
 4. Observe graphs/tables refresh after each click</t>
   </si>
   <si>
-    <t xml:space="preserve">Each card click updates corresponding sections
+    <t>Each card click updates corresponding sections
 Charts remain populated after each selection</t>
   </si>
   <si>
@@ -333,12 +337,12 @@
     <t>REG-RO-011 — Revenue Opportunity By Page: graph visible + tooltip on hover</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Locate Revenue Opportunity By Page horizontal bar graph
+    <t>1. Locate Revenue Opportunity By Page horizontal bar graph
 2. Hover a bar/point
 3. Observe tooltip values</t>
   </si>
   <si>
-    <t xml:space="preserve">By Page graph is visible
+    <t>By Page graph is visible
 Tooltip shows revenue values on hover (when data allows)</t>
   </si>
   <si>
@@ -348,13 +352,13 @@
     <t>REG-RO-012 — Revenue Opportunity By Page: legend toggle + context menu</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Toggle a legend item under/near the By Page graph
+    <t>1. Toggle a legend item under/near the By Page graph
 2. Toggle it back
 3. Open chart hamburger/context menu
 4. Dismiss with Escape</t>
   </si>
   <si>
-    <t xml:space="preserve">Legend toggles series visibility
+    <t>Legend toggles series visibility
 Context menu chrome is available</t>
   </si>
   <si>
@@ -364,12 +368,12 @@
     <t>REG-RO-013 — Revenue Opportunity By Platform: hover tooltip + legend</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Locate By Platform bar graph
+    <t>1. Locate By Platform bar graph
 2. Hover for tooltip
 3. Toggle legend item check/uncheck</t>
   </si>
   <si>
-    <t xml:space="preserve">By Platform graph visible
+    <t>By Platform graph visible
 Tooltip/legend interactions refresh presentation</t>
   </si>
   <si>
@@ -379,7 +383,7 @@
     <t>REG-RO-014 — Revenue Opportunity By Platform: context menu</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Open hamburger/context menu on By Platform graph
+    <t>1. Open hamburger/context menu on By Platform graph
 2. Dismiss menu</t>
   </si>
   <si>
@@ -389,24 +393,24 @@
     <t>REG-RO-015 — Total Actual Revenue: hover tooltip + context menu</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Locate Total Actual Revenue bar graph
+    <t>1. Locate Total Actual Revenue bar graph
 2. Hover for exact values
 3. Open context menu and dismiss</t>
   </si>
   <si>
-    <t xml:space="preserve">Graph visible
+    <t>Graph visible
 Tooltip/menu interactions succeed or page stays healthy</t>
   </si>
   <si>
     <t>REG-RO-016 — All Browser Devices 30 days: line graph hover + legend</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Locate All Browser Devices / Actual Sales Over Time line graph
+    <t>1. Locate All Browser Devices / Actual Sales Over Time line graph
 2. Hover a point for day revenue
 3. Toggle legend; open context menu</t>
   </si>
   <si>
-    <t xml:space="preserve">Line graph visible
+    <t>Line graph visible
 Hover/legend/menu behaviors work as available</t>
   </si>
   <si>
@@ -416,11 +420,11 @@
     <t>REG-RO-017 — What If table visible with optimized/faster columns</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Scroll to What If table
+    <t>1. Scroll to What If table
 2. Confirm columns for optimized / Ns faster opportunity</t>
   </si>
   <si>
-    <t xml:space="preserve">What If / business overview table is visible
+    <t>What If / business overview table is visible
 Fully Optimized / What If faster columns are present</t>
   </si>
   <si>
@@ -430,12 +434,12 @@
     <t>REG-RO-018 — What If: edit variables then Cancel (no Save)</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Hover What If variables and click pencil/edit
+    <t>1. Hover What If variables and click pencil/edit
 2. Change a sample second increment if editable
 3. Click Cancel (do NOT Save)</t>
   </si>
   <si>
-    <t xml:space="preserve">Edit UI opens
+    <t>Edit UI opens
 Cancel discards changes
 No persistent What If Save is performed (read-only automation rule)</t>
   </si>
@@ -446,11 +450,11 @@
     <t>REG-RO-019 — Column sort</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click a sortable column header (Page Name / Fully Optimized / Total Opportunity)
+    <t>1. Click a sortable column header (Page Name / Fully Optimized / Total Opportunity)
 2. Observe row order change</t>
   </si>
   <si>
-    <t xml:space="preserve">Column sort is applied
+    <t>Column sort is applied
 Table remains visible</t>
   </si>
   <si>
@@ -460,11 +464,11 @@
     <t>REG-RO-020 — Search/filter</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Use table search or column filter input
+    <t>1. Use table search or column filter input
 2. Enter a sample term</t>
   </si>
   <si>
-    <t xml:space="preserve">Search/filter narrows rows when control exists
+    <t>Search/filter narrows rows when control exists
 Table remains healthy</t>
   </si>
   <si>
@@ -474,11 +478,11 @@
     <t>REG-RO-021 — Pager navigation when present</t>
   </si>
   <si>
-    <t xml:space="preserve">1. If pager controls exist, click next
+    <t>1. If pager controls exist, click next
 2. Confirm table still visible</t>
   </si>
   <si>
-    <t xml:space="preserve">Pager advances when available
+    <t>Pager advances when available
 Table remains visible</t>
   </si>
   <si>
@@ -488,11 +492,11 @@
     <t>REG-RO-022 — Information icon tooltips sample</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Locate info icons near labels/fields
+    <t>1. Locate info icons near labels/fields
 2. Hover several icons and read tooltips</t>
   </si>
   <si>
-    <t xml:space="preserve">At least one info icon is hoverable
+    <t>At least one info icon is hoverable
 Tooltip/title text is exposed</t>
   </si>
   <si>
@@ -502,12 +506,12 @@
     <t>REG-RO-023 — View Filters / Hide Filters toggles applied-filter banner</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click View Filters
+    <t>1. Click View Filters
 2. Observe applied filter banner
 3. Click Hide Filters</t>
   </si>
   <si>
-    <t xml:space="preserve">Banner shows/hides
+    <t>Banner shows/hides
 Button label toggles View/Hide Filters</t>
   </si>
   <si>
@@ -517,25 +521,25 @@
     <t>REG-RO-024 — Right-nav Filters: performance metric + visitor type sample</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Open Filters (funnel) top-right
+    <t>1. Open Filters (funnel) top-right
 2. Set Performance Metric = Onload; Visitor Type = New Visitors; Apply
 3. Set Returning Visitors; Apply
 4. Do NOT Save Filter</t>
   </si>
   <si>
-    <t xml:space="preserve">Charts refresh for sampled filter combos
+    <t>Charts refresh for sampled filter combos
 No Save Filter write</t>
   </si>
   <si>
     <t>REG-RO-025 — Report Manager opens (read-only; no delete)</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click Report Manager
+    <t>1. Click Report Manager
 2. Observe panel
 3. Close without deleting reports</t>
   </si>
   <si>
-    <t xml:space="preserve">Report Manager opens
+    <t>Report Manager opens
 No delete/write actions performed</t>
   </si>
   <si>
@@ -545,22 +549,22 @@
     <t>REG-RO-026 — Top-nav right controls visible with tooltips</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Hover Filters / Help Center / User menu (and other right-nav icons)
+    <t>1. Hover Filters / Help Center / User menu (and other right-nav icons)
 2. Confirm tooltips</t>
   </si>
   <si>
-    <t xml:space="preserve">Right-nav controls visible with tooltips
+    <t>Right-nav controls visible with tooltips
 Filters control remains available</t>
   </si>
   <si>
     <t>REG-RO-027 — Common legend check/uncheck refreshes series</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click a Highcharts legend item
+    <t>1. Click a Highcharts legend item
 2. Click again to restore</t>
   </si>
   <si>
-    <t xml:space="preserve">Series visibility toggles
+    <t>Series visibility toggles
 Charts remain populated</t>
   </si>
   <si>
@@ -570,18 +574,18 @@
     <t>REG-RO-028 — Additional UI: opportunity calculator / conversion graphs present</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Locate conversion / opportunity calculator graphs if rendered
+    <t>1. Locate conversion / opportunity calculator graphs if rendered
 2. Confirm visibility</t>
   </si>
   <si>
-    <t xml:space="preserve">Available calculator/conversion graphs are visible
+    <t>Available calculator/conversion graphs are visible
 Main charts still have data</t>
   </si>
   <si>
     <t>REG-RO-029 — Data refresh after device card + data type combo</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Set Revenue Data Type to Web Browser Data
+    <t>1. Set Revenue Data Type to Web Browser Data
 2. Click Desktop then All opportunity cards</t>
   </si>
   <si>
@@ -594,11 +598,11 @@
     <t>REG-RO-030 — Performance re-check after interactions: charts still load</t>
   </si>
   <si>
-    <t xml:space="preserve">1. After prior interactions, poll for chart containers
+    <t>1. After prior interactions, poll for chart containers
 2. Confirm title still Revenue Opportunity</t>
   </si>
   <si>
-    <t xml:space="preserve">Charts remain available within 60s poll
+    <t>Charts remain available within 60s poll
 Page title unchanged</t>
   </si>
   <si>
@@ -608,12 +612,12 @@
     <t>REG-RO-031 — iOS / Android card sample when present</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click iOS opportunity card (if present)
+    <t>1. Click iOS opportunity card (if present)
 2. Click Android opportunity card (if present)
 3. Return to All card</t>
   </si>
   <si>
-    <t xml:space="preserve">Device cards refresh charts when available
+    <t>Device cards refresh charts when available
 All card restores overview</t>
   </si>
   <si>
@@ -623,7 +627,7 @@
     <t>REG-RO-032 — Device overview table follows Desktop card selection</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click Desktop 30 Day Opportunity card
+    <t>1. Click Desktop 30 Day Opportunity card
 2. Confirm desktop business overview table is present</t>
   </si>
   <si>
@@ -636,11 +640,11 @@
     <t>REG-RO-033 — What If Save control present but unused (read-only guard)</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Locate Save What If control if rendered
+    <t>1. Locate Save What If control if rendered
 2. Do NOT click Save</t>
   </si>
   <si>
-    <t xml:space="preserve">Save control may be present
+    <t>Save control may be present
 Automation does not persist What If changes</t>
   </si>
   <si>
@@ -650,7 +654,7 @@
     <t>REG-RO-034 — View Filters banner shows applied filter chip sample</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click View Filters
+    <t>1. Click View Filters
 2. Read applied filter chips (Real User / Time Period / Device / etc.)
 3. Hide Filters</t>
   </si>
@@ -664,7 +668,7 @@
     <t>REG-RO-035 — Revenue Calibration top-nav control is present (tooltip)</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Locate Revenue Calibration control in top-right chrome
+    <t>1. Locate Revenue Calibration control in top-right chrome
 2. Hover and confirm tooltip</t>
   </si>
   <si>
@@ -677,14 +681,14 @@
     <t>REG-RO-036 — Time Period 1 Days: labels + Actual Revenue timeline</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Open Revenue Opportunity (no Bucket Size control on this page)
+    <t>1. Open Revenue Opportunity (no Bucket Size control on this page)
 2. Apply Time Period = 1 Day via matching Report (e.g. "… 1 Day …") or Filters Time Period if available
 3. Confirm Opportunity / Actual Revenue Over Time / What If labels mention 1 Day
 4. Hover Actual Revenue Over Time left→right
 5. Validate Highcharts x-axis day buckets (~1 day steps)</t>
   </si>
   <si>
-    <t xml:space="preserve">Period applied via Report list and/or Filters Time Period only (no Bucket Size)
+    <t>Period applied via Report list and/or Filters Time Period only (no Bucket Size)
 Labels show 1 Day Opportunity / Actual Revenue Over Time period text
 What If / opportunity widgets mention 1 day when present
 Actual Revenue timeline uses ~1-day buckets ending near now
@@ -697,12 +701,12 @@
     <t>REG-RO-037 — Time Period 7 Days: labels + Actual Revenue timeline</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Apply Time Period = 7 Days via Report matching "7 Days" (or Filters)
+    <t>1. Apply Time Period = 7 Days via Report matching "7 Days" (or Filters)
 2. Confirm Opportunity / Actual Revenue / What If period labels
 3. Hover Actual Revenue; validate ~1-day timeline buckets</t>
   </si>
   <si>
-    <t xml:space="preserve">No Bucket Size selection (control not present on Revenue Opportunity)
+    <t>No Bucket Size selection (control not present on Revenue Opportunity)
 Labels and widgets reflect 7 Days
 Actual Revenue timeline remains healthy with day-scale buckets</t>
   </si>
@@ -713,12 +717,12 @@
     <t>REG-RO-038 — Time Period 14 Days: labels + Actual Revenue timeline</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Apply Time Period = 14 Days via Report / Filters
+    <t>1. Apply Time Period = 14 Days via Report / Filters
 2. Confirm period labels on Opportunity, Actual Revenue Over Time, What If
 3. Validate Actual Revenue timeline buckets</t>
   </si>
   <si>
-    <t xml:space="preserve">Period applied without Bucket Size
+    <t>Period applied without Bucket Size
 UI labels mention 14 Days
 Timeline buckets remain ~1 day for multi-day reports</t>
   </si>
@@ -729,13 +733,13 @@
     <t>REG-RO-039 — Time Period 30 days: labels + Actual Revenue timeline</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Apply Time Period = 30 Days via Report matching "30 Days" (common default report)
+    <t>1. Apply Time Period = 30 Days via Report matching "30 Days" (common default report)
 2. Confirm "30 Day Opportunity" and Actual Revenue Over Time period text
 3. Confirm What If widgets mention 30 days when labeled
 4. Hover Actual Revenue; validate day buckets near now</t>
   </si>
   <si>
-    <t xml:space="preserve">30-day report/period applies; no Bucket Size control used
+    <t>30-day report/period applies; no Bucket Size control used
 Opportunity / Actual Revenue / What If labels align with 30 days
 Actual Revenue Over Time uses ~1-day Highcharts buckets ending near local now</t>
   </si>
@@ -761,28 +765,33 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFFFF"/>
-    </font>
-    <font>
-      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -804,6 +813,12 @@
         <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -817,9 +832,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -829,6 +843,11 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1167,9 +1186,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -1177,327 +1196,327 @@
     <col min="4" max="4" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2"/>
-      <c r="C2"/>
-      <c r="D2"/>
-    </row>
-    <row r="3" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+    </row>
+    <row r="3" spans="1:5" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="3" t="s">
+    <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="4" t="s">
+    <row r="5" spans="1:5" s="3" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="B5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>4</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="4" t="s">
+    <row r="6" spans="1:5" s="3" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="B6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>4</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="4" t="s">
+    <row r="7" spans="1:5" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="B7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="3">
         <v>3</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="4" t="s">
+    <row r="8" spans="1:5" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="B8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="3">
         <v>3</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="4" t="s">
+    <row r="9" spans="1:5" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="B9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="3">
         <v>3</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="4" t="s">
+    <row r="10" spans="1:5" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="B10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="3">
         <v>3</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="4" t="s">
+    <row r="11" spans="1:5" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="3">
         <v>2</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="4" t="s">
+    <row r="12" spans="1:5" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="3">
         <v>2</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="4" t="s">
+    <row r="13" spans="1:5" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="3">
         <v>2</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="4" t="s">
+    <row r="14" spans="1:5" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="3">
         <v>2</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="4" t="s">
+    <row r="15" spans="1:5" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="3">
         <v>2</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="4" t="s">
+    <row r="16" spans="1:5" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="3">
         <v>2</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="4" t="s">
+    <row r="17" spans="2:5" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="3">
         <v>1</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="4" t="s">
+    <row r="18" spans="2:5" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="3">
         <v>1</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="4" t="s">
+    <row r="19" spans="2:5" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="3">
         <v>1</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="4" t="s">
+    <row r="20" spans="2:5" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="3">
         <v>1</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="4" t="s">
+    <row r="21" spans="2:5" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="3">
         <v>1</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="4" t="s">
+    <row r="22" spans="2:5" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="3">
         <v>1</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="4" t="s">
+    <row r="23" spans="2:5" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="3">
         <v>1</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="5" t="s">
+    <row r="24" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="4">
         <v>39</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="4" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1507,14 +1526,14 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H40"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1525,1070 +1544,1067 @@
     <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="2" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="B2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="H2" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="B3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="H3" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="B4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="H4" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="B5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="H5" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="B6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="H6" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="B7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="H7" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="B8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="H8" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="B9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="H9" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="B10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="H10" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="4" t="s">
+      <c r="B11" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="H11" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="H11" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="B12" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="H12" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="H12" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="B13" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="H13" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="H13" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="B14" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="H14" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="H14" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="4" t="s">
+      <c r="B15" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="H15" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="H15" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="4" t="s">
+      <c r="B16" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="H16" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="H16" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="4" t="s">
+      <c r="B17" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H17" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="18" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+      <c r="H17" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="4" t="s">
+      <c r="B18" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="H18" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+      <c r="H18" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="4" t="s">
+      <c r="B19" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="H19" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+      <c r="H19" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="4" t="s">
+      <c r="B20" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="H20" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+      <c r="H20" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="4" t="s">
+      <c r="B21" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="H21" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="22" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
+      <c r="H21" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="4" t="s">
+      <c r="B22" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="H22" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
+      <c r="H22" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="4" t="s">
+      <c r="B23" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="H23" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="24" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+      <c r="H23" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="4" t="s">
+      <c r="B24" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="H24" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="25" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="H24" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="4" t="s">
+      <c r="B25" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F25" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="H25" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="26" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+      <c r="H25" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="4" t="s">
+      <c r="B26" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="H26" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="27" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
+      <c r="H26" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="4" t="s">
+      <c r="B27" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="F27" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="H27" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="28" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
+      <c r="H27" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="4" t="s">
+      <c r="B28" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="H28" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="29" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+      <c r="H28" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="4" t="s">
+      <c r="B29" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="F29" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="H29" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="30" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
+      <c r="H29" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="4" t="s">
+      <c r="B30" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="F30" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G30" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="H30" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
+      <c r="H30" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" s="4" t="s">
+      <c r="B31" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="F31" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="H31" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="32" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
+      <c r="H31" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="4" t="s">
+      <c r="B32" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="G32" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="H32" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="33" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
+      <c r="H32" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="4" t="s">
+      <c r="B33" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="F33" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="G33" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="H33" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="34" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
+      <c r="H33" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="4" t="s">
+      <c r="B34" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="G34" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="H34" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="35" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
+      <c r="H34" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="4" t="s">
+      <c r="B35" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="F35" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G35" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="H35" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="36" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+      <c r="H35" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="4" t="s">
+      <c r="B36" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="G36" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="H36" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="37" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
+      <c r="H36" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B37" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D37" s="4" t="s">
+      <c r="B37" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E37" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F37" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="G37" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="H37" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="38" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
+      <c r="H37" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="B38" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D38" s="4" t="s">
+      <c r="B38" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F38" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="G38" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="H38" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="39" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+      <c r="H38" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B39" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D39" s="4" t="s">
+      <c r="B39" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="F39" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="G39" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="H39" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="40" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+      <c r="H39" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" s="3" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B40" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D40" s="4" t="s">
+      <c r="B40" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E40" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="F40" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="G40" s="4" t="s">
+      <c r="G40" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="H40" s="4" t="s">
+      <c r="H40" s="3" t="s">
         <v>59</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="H10:H40">
-      <formula1>"Not Executed,Pass,Fail,Blocked,Skipped"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H2:H40">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H40" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Not Executed,Pass,Fail,Blocked,Skipped"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:1" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>206</v>
       </c>
     </row>
@@ -2624,6 +2640,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/docs/Revenue_Opportunity_Regression.xlsx
+++ b/docs/Revenue_Opportunity_Regression.xlsx
@@ -219,7 +219,7 @@
     <t>Regression</t>
   </si>
   <si>
-    <t>REG-RO-001 — Page loads via menu/route with correct breadcrumb</t>
+    <t>Page loads via menu/route with correct breadcrumb</t>
   </si>
   <si>
     <t xml:space="preserve">1. Login to Blue Triangle portal
@@ -228,15 +228,15 @@
 4. Observe breadcrumb and URL</t>
   </si>
   <si>
-    <t xml:space="preserve">Breadcrumb shows Business Insights / Improve Conversion / Revenue Opportunity
-URL contains business-analytics/revenue-opportunity
-User remains authenticated</t>
+    <t xml:space="preserve">1. Breadcrumb shows Business Insights / Improve Conversion / Revenue Opportunity
+2. URL contains business-analytics/revenue-opportunity
+3. User remains authenticated</t>
   </si>
   <si>
     <t>Pass</t>
   </si>
   <si>
-    <t>REG-RO-002 — Default report/session context renders opportunity widgets</t>
+    <t>Default report/session context renders opportunity widgets</t>
   </si>
   <si>
     <t xml:space="preserve">1. Open Revenue Opportunity
@@ -244,113 +244,113 @@
 3. Observe 30 Day Opportunity cards and charts</t>
   </si>
   <si>
-    <t xml:space="preserve">A default report is selected
-Top opportunity / device cards are visible
-Highcharts containers render with data</t>
+    <t xml:space="preserve">1. A default report is selected
+2. Top opportunity / device cards are visible
+3. Highcharts containers render with data</t>
   </si>
   <si>
     <t>REG-RO-003</t>
   </si>
   <si>
-    <t>REG-RO-003 — Page load performance: title + charts within SLA window</t>
+    <t>Page load performance: title + charts within SLA window</t>
   </si>
   <si>
     <t xml:space="preserve">1. Navigate to Revenue Opportunity from a warm session
 2. Measure time until title and charts are ready</t>
   </si>
   <si>
-    <t xml:space="preserve">Page becomes interactive with charts within 120 seconds
-No blank shell / login redirect</t>
+    <t xml:space="preserve">1. Page becomes interactive with charts within 120 seconds
+2. No blank shell / login redirect</t>
   </si>
   <si>
     <t>REG-RO-004</t>
   </si>
   <si>
-    <t>REG-RO-004 — Revenue Data Type: Web Browser Data refreshes widgets</t>
+    <t>Revenue Data Type: Web Browser Data refreshes widgets</t>
   </si>
   <si>
     <t xml:space="preserve">1. Set Revenue Data Type to Web Browser Data
 2. Wait for widgets/charts to refresh</t>
   </si>
   <si>
-    <t xml:space="preserve">Charts refresh successfully
-Page title remains Revenue Opportunity</t>
+    <t xml:space="preserve">1. Charts refresh successfully
+2. Page title remains Revenue Opportunity</t>
   </si>
   <si>
     <t>REG-RO-005</t>
   </si>
   <si>
-    <t>REG-RO-005 — Revenue Data Type: Native App Data sample</t>
+    <t>Revenue Data Type: Native App Data sample</t>
   </si>
   <si>
     <t xml:space="preserve">1. Set Revenue Data Type to Native App Data (if configured for site)
 2. Observe refresh; if unavailable, fall back to Web Browser Data</t>
   </si>
   <si>
-    <t xml:space="preserve">Native App Data applies when configured OR fallback keeps page healthy
-Charts remain populated</t>
+    <t xml:space="preserve">1. Native App Data applies when configured OR fallback keeps page healthy
+2. Charts remain populated</t>
   </si>
   <si>
     <t>REG-RO-006</t>
   </si>
   <si>
-    <t>REG-RO-006 — Revenue Data Type: Web Browser &amp; Native App combination</t>
+    <t>Revenue Data Type: Web Browser &amp; Native App combination</t>
   </si>
   <si>
     <t xml:space="preserve">1. Select combined Web Browser &amp; Native App data type
 2. Confirm widgets refresh</t>
   </si>
   <si>
-    <t xml:space="preserve">Combined data type applies or safe fallback occurs
-Charts show data</t>
+    <t xml:space="preserve">1. Combined data type applies or safe fallback occurs
+2. Charts show data</t>
   </si>
   <si>
     <t>REG-RO-007</t>
   </si>
   <si>
-    <t>REG-RO-007 — Report Type sample combination refreshes page</t>
+    <t>Report Type sample combination refreshes page</t>
   </si>
   <si>
     <t xml:space="preserve">1. Change Report Type (e.g. Page Name)
 2. Change to another type if available (CWV Selector)</t>
   </si>
   <si>
-    <t xml:space="preserve">Report Type changes refresh page content
-Charts remain healthy</t>
+    <t xml:space="preserve">1. Report Type changes refresh page content
+2. Charts remain healthy</t>
   </si>
   <si>
     <t>REG-RO-008</t>
   </si>
   <si>
-    <t>REG-RO-008 — Report dropdown: switch to second available report</t>
+    <t>Report dropdown: switch to second available report</t>
   </si>
   <si>
     <t xml:space="preserve">1. Open Report dropdown
 2. Select the second listed report (if more than one exists)</t>
   </si>
   <si>
-    <t xml:space="preserve">Selected report loads
-Opportunity widgets refresh</t>
+    <t xml:space="preserve">1. Selected report loads
+2. Opportunity widgets refresh</t>
   </si>
   <si>
     <t>REG-RO-009</t>
   </si>
   <si>
-    <t>REG-RO-009 — Restore primary/default report (index 0)</t>
+    <t>Restore primary/default report (index 0)</t>
   </si>
   <si>
     <t xml:space="preserve">1. Select the first report in the Report list
 2. Confirm default-ish context returns</t>
   </si>
   <si>
-    <t xml:space="preserve">First report is active
-Default opportunity context is visible</t>
+    <t xml:space="preserve">1. First report is active
+2. Default opportunity context is visible</t>
   </si>
   <si>
     <t>REG-RO-010</t>
   </si>
   <si>
-    <t>REG-RO-010 — All / Desktop / Mobile card clicks refresh sections</t>
+    <t>All / Desktop / Mobile card clicks refresh sections</t>
   </si>
   <si>
     <t xml:space="preserve">1. Click All / Browser opportunity card
@@ -359,14 +359,14 @@
 4. Observe graphs/tables refresh after each click</t>
   </si>
   <si>
-    <t xml:space="preserve">Each card click updates corresponding sections
-Charts remain populated after each selection</t>
+    <t xml:space="preserve">1. Each card click updates corresponding sections
+2. Charts remain populated after each selection</t>
   </si>
   <si>
     <t>REG-RO-011</t>
   </si>
   <si>
-    <t>REG-RO-011 — Revenue Opportunity By Page: graph visible + tooltip on hover</t>
+    <t>Revenue Opportunity By Page: graph visible + tooltip on hover</t>
   </si>
   <si>
     <t xml:space="preserve">1. Locate Revenue Opportunity By Page horizontal bar graph
@@ -374,14 +374,14 @@
 3. Observe tooltip values</t>
   </si>
   <si>
-    <t xml:space="preserve">By Page graph is visible
-Tooltip shows revenue values on hover (when data allows)</t>
+    <t xml:space="preserve">1. By Page graph is visible
+2. Tooltip shows revenue values on hover (when data allows)</t>
   </si>
   <si>
     <t>REG-RO-012</t>
   </si>
   <si>
-    <t>REG-RO-012 — Revenue Opportunity By Page: legend toggle + context menu</t>
+    <t>Revenue Opportunity By Page: legend toggle + context menu</t>
   </si>
   <si>
     <t xml:space="preserve">1. Toggle a legend item under/near the By Page graph
@@ -390,14 +390,14 @@
 4. Dismiss with Escape</t>
   </si>
   <si>
-    <t xml:space="preserve">Legend toggles series visibility
-Context menu chrome is available</t>
+    <t xml:space="preserve">1. Legend toggles series visibility
+2. Context menu chrome is available</t>
   </si>
   <si>
     <t>REG-RO-013</t>
   </si>
   <si>
-    <t>REG-RO-013 — Revenue Opportunity By Platform: hover tooltip + legend</t>
+    <t>Revenue Opportunity By Platform: hover tooltip + legend</t>
   </si>
   <si>
     <t xml:space="preserve">1. Locate By Platform bar graph
@@ -405,24 +405,24 @@
 3. Toggle legend item check/uncheck</t>
   </si>
   <si>
-    <t xml:space="preserve">By Platform graph visible
-Tooltip/legend interactions refresh presentation</t>
+    <t xml:space="preserve">1. By Platform graph visible
+2. Tooltip/legend interactions refresh presentation</t>
   </si>
   <si>
     <t>REG-RO-014</t>
   </si>
   <si>
-    <t>REG-RO-014 — Revenue Opportunity By Platform: context menu</t>
+    <t>Revenue Opportunity By Platform: context menu</t>
   </si>
   <si>
     <t xml:space="preserve">1. Open hamburger/context menu on By Platform graph
 2. Dismiss menu</t>
   </si>
   <si>
-    <t>Context menu control is present/usable</t>
-  </si>
-  <si>
-    <t>REG-RO-015 — Total Actual Revenue: hover tooltip + context menu</t>
+    <t>1. Context menu control is present/usable</t>
+  </si>
+  <si>
+    <t>Total Actual Revenue: hover tooltip + context menu</t>
   </si>
   <si>
     <t xml:space="preserve">1. Locate Total Actual Revenue bar graph
@@ -430,11 +430,11 @@
 3. Open context menu and dismiss</t>
   </si>
   <si>
-    <t xml:space="preserve">Graph visible
-Tooltip/menu interactions succeed or page stays healthy</t>
-  </si>
-  <si>
-    <t>REG-RO-016 — All Browser Devices 30 days: line graph hover + legend</t>
+    <t xml:space="preserve">1. Graph visible
+2. Tooltip/menu interactions succeed or page stays healthy</t>
+  </si>
+  <si>
+    <t>All Browser Devices 30 days: line graph hover + legend</t>
   </si>
   <si>
     <t xml:space="preserve">1. Locate All Browser Devices / Actual Sales Over Time line graph
@@ -442,28 +442,28 @@
 3. Toggle legend; open context menu</t>
   </si>
   <si>
-    <t xml:space="preserve">Line graph visible
-Hover/legend/menu behaviors work as available</t>
+    <t xml:space="preserve">1. Line graph visible
+2. Hover/legend/menu behaviors work as available</t>
   </si>
   <si>
     <t>REG-RO-017</t>
   </si>
   <si>
-    <t>REG-RO-017 — What If table visible with optimized/faster columns</t>
+    <t>What If table visible with optimized/faster columns</t>
   </si>
   <si>
     <t xml:space="preserve">1. Scroll to What If table
 2. Confirm columns for optimized / Ns faster opportunity</t>
   </si>
   <si>
-    <t xml:space="preserve">What If / business overview table is visible
-Fully Optimized / What If faster columns are present</t>
+    <t xml:space="preserve">1. What If / business overview table is visible
+2. Fully Optimized / What If faster columns are present</t>
   </si>
   <si>
     <t>REG-RO-018</t>
   </si>
   <si>
-    <t>REG-RO-018 — What If: edit variables then Cancel (no Save)</t>
+    <t>What If: edit variables then Cancel (no Save)</t>
   </si>
   <si>
     <t xml:space="preserve">1. Hover What If variables and click pencil/edit
@@ -471,71 +471,71 @@
 3. Click Cancel (do NOT Save)</t>
   </si>
   <si>
-    <t xml:space="preserve">Edit UI opens
-Cancel discards changes
-No persistent What If Save is performed (read-only automation rule)</t>
+    <t xml:space="preserve">1. Edit UI opens
+2. Cancel discards changes
+3. No persistent What If Save is performed (read-only automation rule)</t>
   </si>
   <si>
     <t>REG-RO-019</t>
   </si>
   <si>
-    <t>REG-RO-019 — Column sort</t>
+    <t>Column sort</t>
   </si>
   <si>
     <t xml:space="preserve">1. Click a sortable column header (Page Name / Fully Optimized / Total Opportunity)
 2. Observe row order change</t>
   </si>
   <si>
-    <t xml:space="preserve">Column sort is applied
-Table remains visible</t>
+    <t xml:space="preserve">1. Column sort is applied
+2. Table remains visible</t>
   </si>
   <si>
     <t>REG-RO-020</t>
   </si>
   <si>
-    <t>REG-RO-020 — Search/filter</t>
+    <t>Search/filter</t>
   </si>
   <si>
     <t xml:space="preserve">1. Use table search or column filter input
 2. Enter a sample term</t>
   </si>
   <si>
-    <t xml:space="preserve">Search/filter narrows rows when control exists
-Table remains healthy</t>
+    <t xml:space="preserve">1. Search/filter narrows rows when control exists
+2. Table remains healthy</t>
   </si>
   <si>
     <t>REG-RO-021</t>
   </si>
   <si>
-    <t>REG-RO-021 — Pager navigation when present</t>
+    <t>Pager navigation when present</t>
   </si>
   <si>
     <t xml:space="preserve">1. If pager controls exist, click next
 2. Confirm table still visible</t>
   </si>
   <si>
-    <t xml:space="preserve">Pager advances when available
-Table remains visible</t>
+    <t xml:space="preserve">1. Pager advances when available
+2. Table remains visible</t>
   </si>
   <si>
     <t>REG-RO-022</t>
   </si>
   <si>
-    <t>REG-RO-022 — Information icon tooltips sample</t>
+    <t>Information icon tooltips sample</t>
   </si>
   <si>
     <t xml:space="preserve">1. Locate info icons near labels/fields
 2. Hover several icons and read tooltips</t>
   </si>
   <si>
-    <t xml:space="preserve">At least one info icon is hoverable
-Tooltip/title text is exposed</t>
+    <t xml:space="preserve">1. At least one info icon is hoverable
+2. Tooltip/title text is exposed</t>
   </si>
   <si>
     <t>REG-RO-023</t>
   </si>
   <si>
-    <t>REG-RO-023 — View Filters / Hide Filters toggles applied-filter banner</t>
+    <t>View Filters / Hide Filters toggles applied-filter banner</t>
   </si>
   <si>
     <t xml:space="preserve">1. Click View Filters
@@ -543,14 +543,14 @@
 3. Click Hide Filters</t>
   </si>
   <si>
-    <t xml:space="preserve">Banner shows/hides
-Button label toggles View/Hide Filters</t>
+    <t xml:space="preserve">1. Banner shows/hides
+2. Button label toggles View/Hide Filters</t>
   </si>
   <si>
     <t>REG-RO-024</t>
   </si>
   <si>
-    <t>REG-RO-024 — Right-nav Filters: performance metric + visitor type sample</t>
+    <t>Right-nav Filters: performance metric + visitor type sample</t>
   </si>
   <si>
     <t xml:space="preserve">1. Open Filters (funnel) top-right
@@ -559,11 +559,11 @@
 4. Do NOT Save Filter</t>
   </si>
   <si>
-    <t xml:space="preserve">Charts refresh for sampled filter combos
-No Save Filter write</t>
-  </si>
-  <si>
-    <t>REG-RO-025 — Report Manager opens (read-only; no delete)</t>
+    <t xml:space="preserve">1. Charts refresh for sampled filter combos
+2. No Save Filter write</t>
+  </si>
+  <si>
+    <t>Report Manager opens (read-only; no delete)</t>
   </si>
   <si>
     <t xml:space="preserve">1. Click Report Manager
@@ -571,77 +571,77 @@
 3. Close without deleting reports</t>
   </si>
   <si>
-    <t xml:space="preserve">Report Manager opens
-No delete/write actions performed</t>
+    <t xml:space="preserve">1. Report Manager opens
+2. No delete/write actions performed</t>
   </si>
   <si>
     <t>REG-RO-026</t>
   </si>
   <si>
-    <t>REG-RO-026 — Top-nav right controls visible with tooltips</t>
+    <t>Top-nav right controls visible with tooltips</t>
   </si>
   <si>
     <t xml:space="preserve">1. Hover Filters / Help Center / User menu (and other right-nav icons)
 2. Confirm tooltips</t>
   </si>
   <si>
-    <t xml:space="preserve">Right-nav controls visible with tooltips
-Filters control remains available</t>
-  </si>
-  <si>
-    <t>REG-RO-027 — Common legend check/uncheck refreshes series</t>
+    <t xml:space="preserve">1. Right-nav controls visible with tooltips
+2. Filters control remains available</t>
+  </si>
+  <si>
+    <t>Common legend check/uncheck refreshes series</t>
   </si>
   <si>
     <t xml:space="preserve">1. Click a Highcharts legend item
 2. Click again to restore</t>
   </si>
   <si>
-    <t xml:space="preserve">Series visibility toggles
-Charts remain populated</t>
+    <t xml:space="preserve">1. Series visibility toggles
+2. Charts remain populated</t>
   </si>
   <si>
     <t>REG-RO-028</t>
   </si>
   <si>
-    <t>REG-RO-028 — Additional UI: opportunity calculator / conversion graphs present</t>
+    <t>Additional UI: opportunity calculator / conversion graphs present</t>
   </si>
   <si>
     <t xml:space="preserve">1. Locate conversion / opportunity calculator graphs if rendered
 2. Confirm visibility</t>
   </si>
   <si>
-    <t xml:space="preserve">Available calculator/conversion graphs are visible
-Main charts still have data</t>
-  </si>
-  <si>
-    <t>REG-RO-029 — Data refresh after device card + data type combo</t>
+    <t xml:space="preserve">1. Available calculator/conversion graphs are visible
+2. Main charts still have data</t>
+  </si>
+  <si>
+    <t>Data refresh after device card + data type combo</t>
   </si>
   <si>
     <t xml:space="preserve">1. Set Revenue Data Type to Web Browser Data
 2. Click Desktop then All opportunity cards</t>
   </si>
   <si>
-    <t>Combined interactions refresh charts without error</t>
+    <t>1. Combined interactions refresh charts without error</t>
   </si>
   <si>
     <t>REG-RO-030</t>
   </si>
   <si>
-    <t>REG-RO-030 — Performance re-check after interactions: charts still load</t>
+    <t>Performance re-check after interactions: charts still load</t>
   </si>
   <si>
     <t xml:space="preserve">1. After prior interactions, poll for chart containers
 2. Confirm title still Revenue Opportunity</t>
   </si>
   <si>
-    <t xml:space="preserve">Charts remain available within 60s poll
-Page title unchanged</t>
+    <t xml:space="preserve">1. Charts remain available within 60s poll
+2. Page title unchanged</t>
   </si>
   <si>
     <t>REG-RO-031</t>
   </si>
   <si>
-    <t>REG-RO-031 — iOS / Android card sample when present</t>
+    <t>iOS / Android card sample when present</t>
   </si>
   <si>
     <t xml:space="preserve">1. Click iOS opportunity card (if present)
@@ -649,41 +649,41 @@
 3. Return to All card</t>
   </si>
   <si>
-    <t xml:space="preserve">Device cards refresh charts when available
-All card restores overview</t>
+    <t xml:space="preserve">1. Device cards refresh charts when available
+2. All card restores overview</t>
   </si>
   <si>
     <t>REG-RO-032</t>
   </si>
   <si>
-    <t>REG-RO-032 — Device overview table follows Desktop card selection</t>
+    <t>Device overview table follows Desktop card selection</t>
   </si>
   <si>
     <t xml:space="preserve">1. Click Desktop 30 Day Opportunity card
 2. Confirm desktop business overview table is present</t>
   </si>
   <si>
-    <t>Desktop overview table is attached/visible after Desktop card click</t>
+    <t>1. Desktop overview table is attached/visible after Desktop card click</t>
   </si>
   <si>
     <t>REG-RO-033</t>
   </si>
   <si>
-    <t>REG-RO-033 — What If Save control present but unused (read-only guard)</t>
+    <t>What If Save control present but unused (read-only guard)</t>
   </si>
   <si>
     <t xml:space="preserve">1. Locate Save What If control if rendered
 2. Do NOT click Save</t>
   </si>
   <si>
-    <t xml:space="preserve">Save control may be present
-Automation does not persist What If changes</t>
+    <t xml:space="preserve">1. Save control may be present
+2. Automation does not persist What If changes</t>
   </si>
   <si>
     <t>REG-RO-034</t>
   </si>
   <si>
-    <t>REG-RO-034 — View Filters banner shows applied filter chip sample</t>
+    <t>View Filters banner shows applied filter chip sample</t>
   </si>
   <si>
     <t xml:space="preserve">1. Click View Filters
@@ -691,26 +691,26 @@
 3. Hide Filters</t>
   </si>
   <si>
-    <t>Banner exposes applied filter labels when shown</t>
+    <t>1. Banner exposes applied filter labels when shown</t>
   </si>
   <si>
     <t>REG-RO-035</t>
   </si>
   <si>
-    <t>REG-RO-035 — Revenue Calibration top-nav control is present (tooltip)</t>
+    <t>Revenue Calibration top-nav control is present (tooltip)</t>
   </si>
   <si>
     <t xml:space="preserve">1. Locate Revenue Calibration control in top-right chrome
 2. Hover and confirm tooltip</t>
   </si>
   <si>
-    <t>Calibration control is visible with a tooltip</t>
+    <t>1. Calibration control is visible with a tooltip</t>
   </si>
   <si>
     <t>REG-RO-036</t>
   </si>
   <si>
-    <t>REG-RO-036 — Time Period 1 Days: labels + Actual Revenue timeline</t>
+    <t>Time Period 1 Days: labels + Actual Revenue timeline</t>
   </si>
   <si>
     <t xml:space="preserve">1. Open Revenue Opportunity (no Bucket Size control on this page)
@@ -720,17 +720,17 @@
 5. Validate Highcharts x-axis day buckets (~1 day steps)</t>
   </si>
   <si>
-    <t xml:space="preserve">Period applied via Report list and/or Filters Time Period only (no Bucket Size)
-Labels show 1 Day Opportunity / Actual Revenue Over Time period text
-What If / opportunity widgets mention 1 day when present
-Actual Revenue timeline uses ~1-day buckets ending near now
-If no 1-day report exists on the site, soft-skip with note</t>
+    <t xml:space="preserve">1. Period applied via Report list and/or Filters Time Period only (no Bucket Size)
+2. Labels show 1 Day Opportunity / Actual Revenue Over Time period text
+3. What If / opportunity widgets mention 1 day when present
+4. Actual Revenue timeline uses ~1-day buckets ending near now
+5. If no 1-day report exists on the site, soft-skip with note</t>
   </si>
   <si>
     <t>REG-RO-037</t>
   </si>
   <si>
-    <t>REG-RO-037 — Time Period 7 Days: labels + Actual Revenue timeline</t>
+    <t>Time Period 7 Days: labels + Actual Revenue timeline</t>
   </si>
   <si>
     <t xml:space="preserve">1. Apply Time Period = 7 Days via Report matching "7 Days" (or Filters)
@@ -738,15 +738,15 @@
 3. Hover Actual Revenue; validate ~1-day timeline buckets</t>
   </si>
   <si>
-    <t xml:space="preserve">No Bucket Size selection (control not present on Revenue Opportunity)
-Labels and widgets reflect 7 Days
-Actual Revenue timeline remains healthy with day-scale buckets</t>
+    <t xml:space="preserve">1. No Bucket Size selection (control not present on Revenue Opportunity)
+2. Labels and widgets reflect 7 Days
+3. Actual Revenue timeline remains healthy with day-scale buckets</t>
   </si>
   <si>
     <t>REG-RO-038</t>
   </si>
   <si>
-    <t>REG-RO-038 — Time Period 14 Days: labels + Actual Revenue timeline</t>
+    <t>Time Period 14 Days: labels + Actual Revenue timeline</t>
   </si>
   <si>
     <t xml:space="preserve">1. Apply Time Period = 14 Days via Report / Filters
@@ -754,15 +754,15 @@
 3. Validate Actual Revenue timeline buckets</t>
   </si>
   <si>
-    <t xml:space="preserve">Period applied without Bucket Size
-UI labels mention 14 Days
-Timeline buckets remain ~1 day for multi-day reports</t>
+    <t xml:space="preserve">1. Period applied without Bucket Size
+2. UI labels mention 14 Days
+3. Timeline buckets remain ~1 day for multi-day reports</t>
   </si>
   <si>
     <t>REG-RO-039</t>
   </si>
   <si>
-    <t>REG-RO-039 — Time Period 30 days: labels + Actual Revenue timeline</t>
+    <t>Time Period 30 days: labels + Actual Revenue timeline</t>
   </si>
   <si>
     <t xml:space="preserve">1. Apply Time Period = 30 Days via Report matching "30 Days" (common default report)
@@ -771,12 +771,13 @@
 4. Hover Actual Revenue; validate day buckets near now</t>
   </si>
   <si>
-    <t xml:space="preserve">30-day report/period applies; no Bucket Size control used
-Opportunity / Actual Revenue / What If labels align with 30 days
-Actual Revenue Over Time uses ~1-day Highcharts buckets ending near local now</t>
-  </si>
-  <si>
-    <t>REG-RO-040 — Revenue Data Type, Report Type and Report options are unique and non-blank</t>
+    <t xml:space="preserve">1. 30-day report/period applies
+2. no Bucket Size control used
+3. Opportunity / Actual Revenue / What If labels align with 30 days
+4. Actual Revenue Over Time uses ~1-day Highcharts buckets ending near local now</t>
+  </si>
+  <si>
+    <t>Revenue Data Type, Report Type and Report options are unique and non-blank</t>
   </si>
   <si>
     <t xml:space="preserve">1. Enumerate Revenue Data Type options
@@ -784,22 +785,22 @@
 3. Enumerate Report options</t>
   </si>
   <si>
-    <t xml:space="preserve">Each required selector has options
-Enabled labels are non-blank and not duplicated</t>
-  </si>
-  <si>
-    <t>REG-RO-041 — Visible cards expose device/platform labels and formatted values</t>
+    <t xml:space="preserve">1. Each required selector has options
+2. Enabled labels are non-blank and not duplicated</t>
+  </si>
+  <si>
+    <t>Visible cards expose device/platform labels and formatted values</t>
   </si>
   <si>
     <t xml:space="preserve">1. Read all visible opportunity cards
 2. Validate each label and value/no-data presentation</t>
   </si>
   <si>
-    <t xml:space="preserve">At least one card is visible
-Cards identify device/platform and display a value or controlled no-data state</t>
-  </si>
-  <si>
-    <t>REG-RO-042 — Rapid device-card changes resolve without duplicate chart hosts</t>
+    <t xml:space="preserve">1. At least one card is visible
+2. Cards identify device/platform and display a value or controlled no-data state</t>
+  </si>
+  <si>
+    <t>Rapid device-card changes resolve without duplicate chart hosts</t>
   </si>
   <si>
     <t xml:space="preserve">1. Rapidly select each visible device card
@@ -807,15 +808,15 @@
 3. Inspect chart host IDs</t>
   </si>
   <si>
-    <t xml:space="preserve">Final selection resolves
-Charts remain healthy
-No duplicate chart host IDs are rendered</t>
+    <t xml:space="preserve">1. Final selection resolves
+2. Charts remain healthy
+3. No duplicate chart host IDs are rendered</t>
   </si>
   <si>
     <t>REG-RO-043</t>
   </si>
   <si>
-    <t>REG-RO-043 — What If selectors expose valid ranges and Cancel restores values</t>
+    <t>What If selectors expose valid ranges and Cancel restores values</t>
   </si>
   <si>
     <t xml:space="preserve">1. Open What If edit mode
@@ -824,15 +825,15 @@
 4. Click Cancel; never Save</t>
   </si>
   <si>
-    <t xml:space="preserve">All configured option lists are non-blank/unique
-Cancel restores original values
-No persistent change is made</t>
+    <t xml:space="preserve">1. All configured option lists are non-blank/unique
+2. Cancel restores original values
+3. No persistent change is made</t>
   </si>
   <si>
     <t>REG-RO-044</t>
   </si>
   <si>
-    <t>REG-RO-044 — No-match table search and clear preserve a healthy table</t>
+    <t>No-match table search and clear preserve a healthy table</t>
   </si>
   <si>
     <t xml:space="preserve">1. Enter a guaranteed no-match search value
@@ -840,14 +841,14 @@
 3. Clear the search</t>
   </si>
   <si>
-    <t xml:space="preserve">Table remains visible during no-match state
-Clearing search restores the table without error</t>
+    <t xml:space="preserve">1. Table remains visible during no-match state
+2. Clearing search restores the table without error</t>
   </si>
   <si>
     <t>REG-RO-045</t>
   </si>
   <si>
-    <t>REG-RO-045 — Advanced Filters expose labels and Cancel without applying</t>
+    <t>Advanced Filters expose labels and Cancel without applying</t>
   </si>
   <si>
     <t xml:space="preserve">1. Open the advanced Filters drawer
@@ -855,37 +856,37 @@
 3. Click Cancel or Escape</t>
   </si>
   <si>
-    <t xml:space="preserve">Configured filter fields are labeled
-Cancel closes without applying a new filter</t>
+    <t xml:space="preserve">1. Configured filter fields are labeled
+2. Cancel closes without applying a new filter</t>
   </si>
   <si>
     <t>REG-RO-046</t>
   </si>
   <si>
-    <t>REG-RO-046 — Core controls expose accessible names</t>
+    <t>Core controls expose accessible names</t>
   </si>
   <si>
     <t xml:space="preserve">1. Inspect Revenue Data Type, Report, View Filters, Report Manager and Filters
 2. Read labels/ARIA/title metadata</t>
   </si>
   <si>
-    <t>Each configured core control exposes an accessible label or name</t>
+    <t>1. Each configured core control exposes an accessible label or name</t>
   </si>
   <si>
     <t>REG-RO-047</t>
   </si>
   <si>
-    <t>REG-RO-047 — Keyboard focus reaches interactive page controls</t>
+    <t>Keyboard focus reaches interactive page controls</t>
   </si>
   <si>
     <t xml:space="preserve">1. Focus visible top controls, chart buttons and table search
 2. Confirm document active element updates</t>
   </si>
   <si>
-    <t>At least one representative Revenue Opportunity control receives keyboard focus</t>
-  </si>
-  <si>
-    <t>REG-RO-048 — Standard and narrow desktop viewports retain essential controls</t>
+    <t>1. At least one representative Revenue Opportunity control receives keyboard focus</t>
+  </si>
+  <si>
+    <t>Standard and narrow desktop viewports retain essential controls</t>
   </si>
   <si>
     <t xml:space="preserve">1. Set 1280×800 viewport
@@ -893,14 +894,14 @@
 3. Verify title, selectors, cards and charts</t>
   </si>
   <si>
-    <t xml:space="preserve">Essential controls remain present and reachable
-Charts remain healthy after viewport restoration</t>
+    <t xml:space="preserve">1. Essential controls remain present and reachable
+2. Charts remain healthy after viewport restoration</t>
   </si>
   <si>
     <t>REG-RO-049</t>
   </si>
   <si>
-    <t>REG-RO-049 — Selected report refresh behavior is controlled and recoverable</t>
+    <t>Selected report refresh behavior is controlled and recoverable</t>
   </si>
   <si>
     <t xml:space="preserve">1. Select a second report when available
@@ -909,11 +910,11 @@
 4. Restore first report</t>
   </si>
   <si>
-    <t xml:space="preserve">Refresh preserves the selected report or safely returns to a configured default
-Default report is recoverable</t>
-  </si>
-  <si>
-    <t>REG-RO-050 — Final recovery restores default context without blocking page errors</t>
+    <t xml:space="preserve">1. Refresh preserves the selected report or safely returns to a configured default
+2. Default report is recoverable</t>
+  </si>
+  <si>
+    <t>Final recovery restores default context without blocking page errors</t>
   </si>
   <si>
     <t xml:space="preserve">1. Close open overlays
@@ -921,8 +922,8 @@
 3. Inspect captured page errors and chart IDs</t>
   </si>
   <si>
-    <t xml:space="preserve">Default healthy context is restored
-No duplicate charts or unexpected blocking page errors remain</t>
+    <t xml:space="preserve">1. Default healthy context is restored
+2. No duplicate charts or unexpected blocking page errors remain</t>
   </si>
   <si>
     <t>Blue Triangle Portal — Revenue Opportunity Regression Test Cases</t>
@@ -931,22 +932,22 @@
     <t>Profile / Site: US — GDC Test Site 2</t>
   </si>
   <si>
-    <t>Type: Regression (read-only). Do NOT Save What If, Save Filter, or delete reports.</t>
+    <t>Type: Regression (read-only). Prefer live UI; do not assert exact backend numeric values unless specified.</t>
   </si>
   <si>
     <t>Columns: Test Case ID | Type | Module | Submodule | Title | Steps | Expected Results | Status</t>
   </si>
   <si>
-    <t>Total cases: 50</t>
+    <t>Header style: bold white text on #1F4E79</t>
+  </si>
+  <si>
+    <t>Total cases: 50 (REG-RO-001 .. REG-RO-050)</t>
   </si>
   <si>
     <t>Automation: tests/regression_tests/US2/business-insights/improve-conversion/revenue-opportunity/revenue.opportunity.regression.spec.ts</t>
   </si>
   <si>
     <t>Execution status: Pass</t>
-  </si>
-  <si>
-    <t>Execution note: Executed 2026-07-30 against US / GDC Test Site 2: 50 Revenue Opportunity regression tests plus authentication setup passed; conditional data/configuration paths are recorded as Allure annotations.</t>
   </si>
 </sst>
 </file>
@@ -1011,15 +1012,17 @@
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1365,7 +1368,7 @@
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="70" customWidth="1"/>
+    <col min="4" max="4" width="72" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1377,402 +1380,402 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2"/>
-      <c r="C2"/>
-      <c r="D2"/>
-    </row>
-    <row r="3" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" ht="22" customHeight="1" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="3" t="s">
+    <row r="4" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="4" t="s">
+    <row r="5" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="5">
         <v>5</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="4" t="s">
+    <row r="6" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="5">
         <v>4</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="4" t="s">
+    <row r="7" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="5">
         <v>4</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="4" t="s">
+    <row r="8" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="5">
         <v>4</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="4" t="s">
+    <row r="9" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="5">
         <v>4</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="4" t="s">
+    <row r="10" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="5">
         <v>3</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="4" t="s">
+    <row r="11" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="5">
         <v>2</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="4" t="s">
+    <row r="12" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="5">
         <v>2</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="4" t="s">
+    <row r="13" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="5">
         <v>2</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="4" t="s">
+    <row r="14" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="5">
         <v>2</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="4" t="s">
+    <row r="15" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="5">
         <v>2</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="4" t="s">
+    <row r="16" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="5">
         <v>2</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="4" t="s">
+    <row r="17" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="5">
         <v>2</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="4" t="s">
+    <row r="18" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="5">
         <v>1</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="4" t="s">
+    <row r="19" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="5">
         <v>1</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="4" t="s">
+    <row r="20" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="5">
         <v>1</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="4" t="s">
+    <row r="21" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="5">
         <v>1</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="4" t="s">
+    <row r="22" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="5">
         <v>1</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="4" t="s">
+    <row r="23" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="5">
         <v>1</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="4" t="s">
+    <row r="24" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="5">
         <v>1</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="4" t="s">
+    <row r="25" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="5">
         <v>1</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="5" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="4" t="s">
+    <row r="26" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="5">
         <v>1</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="4" t="s">
+    <row r="27" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="5">
         <v>1</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="4" t="s">
+    <row r="28" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="5">
         <v>1</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="4" t="s">
+    <row r="29" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="5">
         <v>1</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="5" t="s">
+    <row r="30" spans="2:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D30" s="6">
         <v>50</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="6" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1791,1338 +1794,1339 @@
   <dimension ref="A1:H51"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="62" customWidth="1"/>
-    <col min="6" max="7" width="68" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="58" customWidth="1"/>
+    <col min="6" max="6" width="68" customWidth="1"/>
+    <col min="7" max="7" width="62" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="2" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" ht="76" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="B2" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="H2" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="B3" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="H3" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="B4" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="5" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="H4" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="B5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="6" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="H5" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="B6" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="H6" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="B7" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="H7" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="B8" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="H8" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="B9" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="H9" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="B10" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="H10" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" ht="76" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="4" t="s">
+      <c r="B11" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="H11" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="H11" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="B12" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="H12" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="H12" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" ht="76" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="B13" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="H13" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="14" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="H13" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="B14" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="H14" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="H14" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="4" t="s">
+      <c r="B15" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="H15" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="H15" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="4" t="s">
+      <c r="B16" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="H16" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="H16" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="4" t="s">
+      <c r="B17" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="H17" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="18" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+      <c r="H17" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="4" t="s">
+      <c r="B18" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="H18" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+      <c r="H18" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="4" t="s">
+      <c r="B19" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="H19" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="20" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+      <c r="H19" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="4" t="s">
+      <c r="B20" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="H20" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="21" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+      <c r="H20" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="4" t="s">
+      <c r="B21" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="H21" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="22" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
+      <c r="H21" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="4" t="s">
+      <c r="B22" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="H22" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
+      <c r="H22" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="4" t="s">
+      <c r="B23" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="H23" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="24" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+      <c r="H23" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="4" t="s">
+      <c r="B24" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="H24" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="H24" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" ht="76" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="4" t="s">
+      <c r="B25" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F25" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="H25" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="26" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+      <c r="H25" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="4" t="s">
+      <c r="B26" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="H26" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="27" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
+      <c r="H26" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="4" t="s">
+      <c r="B27" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="F27" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="H27" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="28" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
+      <c r="H27" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="4" t="s">
+      <c r="B28" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="H28" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="29" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+      <c r="H28" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="4" t="s">
+      <c r="B29" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="F29" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="H29" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="30" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
+      <c r="H29" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="4" t="s">
+      <c r="B30" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="F30" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G30" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="H30" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="31" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
+      <c r="H30" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" s="4" t="s">
+      <c r="B31" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="F31" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="H31" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="32" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
+      <c r="H31" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" ht="60" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="4" t="s">
+      <c r="B32" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="G32" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="H32" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="33" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
+      <c r="H32" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="4" t="s">
+      <c r="B33" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="F33" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="G33" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="H33" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="34" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
+      <c r="H33" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="4" t="s">
+      <c r="B34" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="G34" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="H34" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="35" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
+      <c r="H34" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="4" t="s">
+      <c r="B35" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="F35" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G35" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="H35" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="36" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+      <c r="H35" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="4" t="s">
+      <c r="B36" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="G36" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="H36" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="37" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
+      <c r="H36" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" ht="92" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="B37" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D37" s="4" t="s">
+      <c r="B37" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E37" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F37" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="G37" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="H37" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="38" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
+      <c r="H37" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="B38" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D38" s="4" t="s">
+      <c r="B38" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F38" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="G38" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="H38" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="39" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+      <c r="H38" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="B39" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D39" s="4" t="s">
+      <c r="B39" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="F39" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="G39" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="H39" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="40" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+      <c r="H39" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="40" ht="76" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="B40" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D40" s="4" t="s">
+      <c r="B40" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E40" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="F40" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="G40" s="4" t="s">
+      <c r="G40" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="H40" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="41" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
+      <c r="H40" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="41" ht="60" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B41" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D41" s="4" t="s">
+      <c r="B41" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="E41" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="F41" s="4" t="s">
+      <c r="F41" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="G41" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="H41" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="42" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
+      <c r="H41" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="42" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B42" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D42" s="4" t="s">
+      <c r="B42" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="E42" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="F42" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="G42" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="H42" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="43" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
+      <c r="H42" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="43" ht="60" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B43" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D43" s="4" t="s">
+      <c r="B43" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E43" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F43" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="G43" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="H43" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="44" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
+      <c r="H43" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="44" ht="76" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="B44" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" s="4" t="s">
+      <c r="B44" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="F44" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="G44" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="H44" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="45" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="4" t="s">
+      <c r="H44" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="45" ht="60" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="B45" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" s="4" t="s">
+      <c r="B45" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="E45" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="F45" s="4" t="s">
+      <c r="F45" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="G45" s="4" t="s">
+      <c r="G45" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="H45" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="46" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
+      <c r="H45" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="46" ht="60" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="B46" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D46" s="4" t="s">
+      <c r="B46" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E46" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="F46" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="G46" s="4" t="s">
+      <c r="G46" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="H46" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="47" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="4" t="s">
+      <c r="H46" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="47" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="B47" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D47" s="4" t="s">
+      <c r="B47" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="E47" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="F47" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="G47" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="H47" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="48" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
+      <c r="H47" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="48" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="B48" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D48" s="4" t="s">
+      <c r="B48" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="E48" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="F48" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="G48" s="4" t="s">
+      <c r="G48" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="H48" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="49" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
+      <c r="H48" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="49" ht="60" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B49" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D49" s="4" t="s">
+      <c r="B49" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E49" s="4" t="s">
+      <c r="E49" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="F49" s="4" t="s">
+      <c r="F49" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="G49" s="4" t="s">
+      <c r="G49" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="H49" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="50" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
+      <c r="H49" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="50" ht="76" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="B50" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D50" s="4" t="s">
+      <c r="B50" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E50" s="4" t="s">
+      <c r="E50" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="F50" s="4" t="s">
+      <c r="F50" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="G50" s="4" t="s">
+      <c r="G50" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="H50" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="51" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
+      <c r="H50" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="51" ht="60" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B51" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" s="4" t="s">
+      <c r="B51" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E51" s="4" t="s">
+      <c r="E51" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="F51" s="4" t="s">
+      <c r="F51" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="G51" s="4" t="s">
+      <c r="G51" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="H51" s="4" t="s">
+      <c r="H51" s="5" t="s">
         <v>71</v>
       </c>
     </row>
@@ -3148,8 +3152,8 @@
     <col min="1" max="1" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>257</v>
       </c>
     </row>
@@ -3175,17 +3179,17 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1</v>
+        <v>262</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>263</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
